--- a/important_mails_2026-10-14.xlsx
+++ b/important_mails_2026-10-14.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H245"/>
+  <dimension ref="A1:H244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,21 +500,74 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Wed, 14 Oct 2026 05:11:00 +0000</t>
+          <t>Wed, 14 Oct 2026 16:23:15 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>FBA reimbursement notification</t>
+          <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai US,
+The following automated unfulfillable FBA removal orders have been created based on your automated settings.
+ Removal order ID gi5Nvepbep
+ You can view the removals on Removal Order Details in your seller account by using the Search tool.
+The next removal order will be created as scheduled on October 15, 2026 in accordance with your settings if you have unfulfillable inventory at that time.
+To make changes to the shipping address, frequency of your automated unfulfillable removals, or other settings, go to Automated unfulfillable removal settings in your seller account.
+ Thank you.
+The Fulfillment by Amazon team
+Please note: This email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferences
+ Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
+ Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
+ SPC-USAmazon-263885051523400</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 14 Oct 2026 05:11:00 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -530,40 +583,89 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 14 Oct 2026 17:02:54 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Tu pago está en camino</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+This title will display on mobile devices
+ ¡Enhorabuena! El pago está de camino y llegará pronto.
+ El pago está en camino
+Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de De 3 a 5 días.
+El 10/14/26 17:02 WEST, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
+ 206,48.
+ Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
+ ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
+ ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
+Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
+Te deseamos un éxito </t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Wed, 14 Oct 2026 04:11:58 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Reactiva tus listings en la UE: se requiere el cumplimiento del
  Reglamento relativo a la seguridad general de los productos</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>96
  Reactiva tus listings en la UE: se requiere el cumplimiento del Reglamento relativo a la seguridad general de los productos
@@ -581,39 +683,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 17:44:30 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Xqa6kjy120)</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -633,39 +735,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 05:11:27 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -681,39 +783,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Sun, 11 Oct 2026 09:31:41 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -729,39 +831,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Sun, 11 Oct 2026 04:46:33 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -777,39 +879,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Sat, 10 Oct 2026 14:54:13 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>"Amazon.ca" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>96
 Balance paid on your Amazon seller account
@@ -830,39 +932,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Sat, 10 Oct 2026 04:49:48 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -878,39 +980,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Sat, 10 Oct 2026 00:57:30 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 Balance paid on your Amazon seller account
@@ -928,39 +1030,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Fri, 9 Oct 2026 05:03:27 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -976,39 +1078,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Thu, 8 Oct 2026 16:07:57 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Multichannel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF
 As a valued Multichannel Fulfillment (MCF) managed customer, we are interested in learning about your program feedback including new features that may benefit your business. This may help us understand how we can better meet your business needs and continue to improve the customer experience.
@@ -1022,39 +1124,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 05:15:33 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 145 PCS Eisenbahn Elektrisch Cube Track, 3D Schwerkrafttrotzendes Zug Set, DIY Zugstrecken Spielzeug, STEM Lernspielzeug &amp;amp; Geschenkidee für Kinder 3–8 Jahre, Kreatives Bauen Spielzeug
@@ -1075,39 +1177,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Tue, 13 Oct 2026 15:42:16 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1127,39 +1229,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Tue, 13 Oct 2026 13:49:53 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Negatieve saldoaanpassing voor al je accounts</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1176,39 +1278,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 20:13:21 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Descargar el informe fiscal de China de abril a junio de 2026</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
  Ya puedes descargar tu declaración fiscal trimestral, que incluye datos como información de identidad, número de transacciones, ingresos y tarifas por servicios y comisiones.
@@ -1224,39 +1326,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 14:55:18 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for January–March 2026</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report, which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -1272,39 +1374,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 14:51:43 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for January - March 2026</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -1320,39 +1422,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Sat, 10 Oct 2026 13:43:05 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>欧洲亚马逊 Payments &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>跨账户负余额调整</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1372,39 +1474,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Thu, 8 Oct 2026 12:48:14 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europa &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Ajuste de saldo negativo en tus cuentas de Vender en Amazon</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1428,95 +1530,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 7 Oct 2026 14:20:27 +0000</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Rettifica del saldo negativo nei tuoi account</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Abbiamo rettificato il tuo saldo negativo di 31.62 € dovuto dal tuo account venditore Amazon.it in data ottobre 7, 2026, utilizzando i fondi disponibili nel tuo account Amazon.fr. Puoi visualizzare il saldo del tuo account in qualsiasi momento accedendo al tuo account e quindi alla dashboard dei pagamenti .
-Per maggiori informazioni, vai a Rettifica del saldo negativo nei tuoi account .
-Distinti saluti,
-Amazon Payments Europe
- Segnala un problema con questa e-mail
- Per qualsiasi domanda consulta: Seller Central
- Per modificare le preferenze sulle e-mail consulta: Preferenze sulle notifiche
- Copyright 2026 Amazon, Inc. o società affiliate. Tutti i diritti riservati.
- Amazon Payments Europe
- 38 avenue John F. Kennedy,
- L-1855 Lussemburgo,
- Numero di registrazione in Lussemburgo: B-101818,
- Capitale Sociale 165.833 EUR,
- Numero di licenza di attività commerciale: 134248,
- Partita IVA n. LU 20260743.
- Questa e-mail è stata inviata da un indirizzo e-mail non monitorato.
- SPC-EUAmazon-1600890628109755</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Tue, 13 Oct 2026 01:19:09 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1534,39 +1580,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 17:16:17 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1584,39 +1630,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 08:57:55 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Reactivate your EU listings - GPSR compliance required</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Reactivate your EU listings - GPSR compliance required
@@ -1636,39 +1682,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 01:16:04 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1686,39 +1732,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Sun, 11 Oct 2026 17:11:11 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1736,39 +1782,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Sun, 11 Oct 2026 16:03:12 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1786,39 +1832,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Fri, 9 Oct 2026 07:35:36 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  96
@@ -1845,39 +1891,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Thu, 8 Oct 2026 13:20:34 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1895,39 +1941,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Thu, 8 Oct 2026 12:56:57 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -1943,39 +1989,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Thu, 8 Oct 2026 11:25:17 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1993,60 +2039,10 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 7 Oct 2026 13:15:21 +0000</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai EU,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listing?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
--
- If you believe that your products are exempt from these requirements, submit documentation demonstrating why they are not subj</t>
-        </is>
-      </c>
-    </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2061,7 +2057,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Wed, 7 Oct 2026 11:16:06 +0000</t>
+          <t>Tue, 13 Oct 2026 09:09:18 +0000</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2071,111 +2067,11 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Submit product safety documentation to reactivate listings</t>
+          <t>Umożliw ponowną aktywację ofert w UE – wymagana zgodność z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai EU,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 7 Oct 2026 10:16:15 +0000</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai EU,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 13 Oct 2026 09:09:18 +0000</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Umożliw ponowną aktywację ofert w UE – wymagana zgodność z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>96
  Umożliw ponowną aktywację ofert w UE – wymagana zgodność z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów
@@ -2193,39 +2089,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Tue, 13 Oct 2026 04:11:35 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>96
  Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs
@@ -2244,39 +2140,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 23:54:30 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>96
  Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
@@ -2295,39 +2191,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 19:58:04 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Réactivez vos mises en vente dans l’UE – Conformité au RSGP requise</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
  Réactivez vos mises en vente dans l’UE – Conformité au RSGP requise
@@ -2346,39 +2242,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 14:31:33 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Activeer je EU-productvermeldingen opnieuw - VAPV-naleving vereist</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Activeer je EU-productvermeldingen opnieuw - VAPV-naleving vereist
@@ -2397,39 +2293,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 08:28:39 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -2445,40 +2341,40 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 08:17:00 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Tu cuenta cumple ahora nuestros requisitos de registro a efectos
  fiscales en Europa</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
  Tu cuenta cumple ahora nuestros requisitos de registro a efectos fiscales en Europa
@@ -2504,39 +2400,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 08:12:09 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Twoje konto spełnia już europejskie wymagania Amazon dotyczące rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
  Twoje konto spełnia już europejskie wymagania Amazon dotyczące rejestracji jako podatnik VAT
@@ -2562,40 +2458,40 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 05:19:47 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -2611,39 +2507,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 03:59:49 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Umożliw ponowną aktywację ofert w UE – wymagana zgodność z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
  Umożliw ponowną aktywację ofert w UE – wymagana zgodność z rozporządzeniem w sprawie ogólnego bezpieczeństwa produktów
@@ -2661,39 +2557,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Sun, 11 Oct 2026 22:52:35 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
  Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs
@@ -2712,39 +2608,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Sun, 11 Oct 2026 18:40:34 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
  Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
@@ -2763,39 +2659,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Sun, 11 Oct 2026 15:54:38 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -2811,39 +2707,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Sun, 11 Oct 2026 14:11:40 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  尊敬的 Weihai EU：
@@ -2885,40 +2781,40 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Sun, 11 Oct 2026 12:18:00 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -2934,39 +2830,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Sun, 11 Oct 2026 08:43:36 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -2982,39 +2878,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Sun, 11 Oct 2026 08:19:52 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -3030,39 +2926,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Sat, 10 Oct 2026 00:43:21 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3077,39 +2973,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Fri, 9 Oct 2026 14:58:07 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 9/2026</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 9/2026
  96
@@ -3131,39 +3027,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Thu, 8 Oct 2026 13:20:10 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -3179,39 +3075,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Thu, 8 Oct 2026 09:44:05 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长
 尊敬的卖家，
@@ -3226,39 +3122,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Wed, 7 Oct 2026 17:49:13 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -3272,233 +3168,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 7 Oct 2026 13:15:49 +0000</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>Dien productveiligheidsdocumentatie in om productvermeldingen
- opnieuw te activeren</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
- Hallo Weihai EU,
- Sommige van je productvermeldingen zijn gedeactiveerd omdat er verplichte nalevingsvereisten voor je producten ontbreken. Bekijk de gegevens en de stappen hieronder. De betreffende productvermeldingen worden aan het einde van deze e-mail weergegeven.
- Waarom gebeurt dit?
- We hebben deze actie ondernomen omdat voor deze producten verplichte nalevingsinformatie ontbreekt. Raadpleeg onze hulp-pagina Productveiligheid en -conformiteit voor informatie over de toepasselijke wet- en regelgeving en het Amazon-beleid. We hebben gebruikgemaakt van een combinatie van geautomatiseerde middelen en deskundige menselijke beoordeling om dit probleem te identificeren en deze beslissing te nemen.
- De tabel aan het einde van deze e-mail bevat productspecifieke nalevingsvereisten.
- Hoe activeer ik mijn productvermeldingen opnieuw?
- Als je de vereiste nalevingsgegevens wilt verstrekken, ga je naar de pagina Accountstatus en zoek je de aanvragen voor productconformiteit:
--
- Als je over de vereiste documentatie beschikt, volg je de instructies om je nalevingsdocumenten in te dienen. We zullen alleen </t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 7 Oct 2026 13:15:41 +0000</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>96
- Presenta la documentación sobre seguridad del producto para reactivar los listings
- Hola, Weihai EU:
- Algunos de tus listings se han desactivado debido a que tus productos no cumplen los requisitos obligatorios. Revisa a continuación los detalles y siguientes pasos. Los listings afectados aparecen al final de este correo electrónico.
- ¿A qué se debe esto?
- Tomamos esta medida porque a estos productos les falta información de cumplimiento normativo obligatoria. Para más información sobre las leyes, normativas y políticas de Amazon aplicables, consulta Cumplimiento y seguridad de los productos . Hemos usado una combinación de medios automatizados y revisión humana experta para identificar la incidencia y tomar una decisión.
- En la tabla que aparece al final de este correo electrónico se proporcionan los requisitos de cumplimiento normativo específicos del producto.
- ¿Cómo puedo reactivar mis listings?
- Para proporcionar la información de cumplimiento normativo obligatoria, ve a la página Estado de la cuenta y localiza las solicitudes de cumplimiento normativo del producto:
--
- Si dispones de la documentación obligatoria, sigue las instrucciones para presentar los documentos de cum</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 7 Oct 2026 13:15:40 +0000</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>96
- Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
- Bonjour Weihai EU,
- Certaines de vos mises en vente ont été désactivées, car vos produits ne respectaient pas des exigences de conformité obligatoires. Consultez les détails et les étapes suivantes ci-dessous. Les produits mis en vente concernés figurent à la fin de cet e-mail.
- Pourquoi cela se produit-il ?
- Nous prenons cette mesure, car ces produits ne présentent pas les informations de conformité obligatoires. Consultez notre page d’aide Sécurité et conformité des produits pour obtenir des informations sur les lois, réglementations et politiques Amazon applicables. Nous nous sommes appuyés sur une combinaison de moyens automatisés et de contrôles menés par des personnes expérimentées pour identifier ce problème et prendre cette décision.
- Le tableau situé à la fin de cet e-mail présente les exigences de conformité spécifiques aux produits.
- Comment réactiver mes produits mis en vente ?
- Pour fournir les informations de conformité requises, accédez à la page État du compte et localisez les demandes de conformité des produits :
--
- Si vous disposez des documents requis, suivez les instructio</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 7 Oct 2026 13:15:09 +0000</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
- le offerte</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>96
- Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
- Gentile Weihai EU,
- Alcune delle tue offerte sono state disattivate a causa della mancanza di alcuni requisiti di conformità obbligatori per i tuoi prodotti. Rivedi i dettagli e i passi successivi riportati di seguito. Puoi visualizzare le offerte interessate in fondo a questa e-mail.
- Ciò a cosa è dovuto?
- Abbiamo intrapreso questo provvedimento in quanto i tuoi prodotti non dispongono delle informazioni obbligatorie sulla conformità. Consulta la pagina di aiuto Sicurezza e conformità dei prodotti per informazioni sulle leggi, le normative e le politiche di Amazon applicabili. Questa decisione è stata presa sulla base dei risultati di un'analisi effettuata in parte tramite revisione umana e in parte per mezzo di sistemi automatizzati.
- La tabella alla fine di questa e-mail contiene i requisiti di conformità specifici per i prodotti.
- Come faccio a riattivare le mie offerte?
- Per fornire le informazioni di conformità richieste, vai alla pagina Stato dell'account per individuare le richieste di conformità dei prodotti:
--
- Se disponi della documentazione richiesta, segui le istruzioni per inviare i do</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Sat, 10 Oct 2026 03:51:55 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-10-22</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -3520,39 +3222,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Sat, 10 Oct 2026 03:37:48 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -3576,39 +3278,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Wed, 7 Oct 2026 05:17:16 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3624,39 +3326,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Tue, 6 Oct 2026 04:57:40 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3672,39 +3374,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Sat, 3 Oct 2026 17:10:17 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3725,39 +3427,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Sat, 3 Oct 2026 04:56:42 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3773,39 +3475,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Fri, 2 Oct 2026 04:48:02 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3821,39 +3523,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Fri, 2 Oct 2026 03:23:37 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Jl40SY3EId)</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3873,39 +3575,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Tue, 29 Sep 2026 19:30:09 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (4sQeBGpWIe)</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3925,39 +3627,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Tue, 29 Sep 2026 09:21:47 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3973,39 +3675,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Tue, 29 Sep 2026 05:14:04 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4021,39 +3723,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Mon, 28 Sep 2026 05:02:53 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4069,39 +3771,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Sun, 27 Sep 2026 23:20:30 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (cENUYoUvou)</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4126,39 +3828,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Sun, 27 Sep 2026 04:48:00 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4174,39 +3876,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 16:39:11 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -4227,39 +3929,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Fri, 25 Sep 2026 04:50:51 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4275,39 +3977,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 04:54:38 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4323,39 +4025,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 16:43:27 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (7iKN0D3u4y)</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4375,39 +4077,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 09:25:48 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4423,39 +4125,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 05:04:18 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4471,39 +4173,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Tue, 22 Sep 2026 14:06:30 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Address variation policy violations</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
  Address variation policy violations
@@ -4519,39 +4221,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Tue, 22 Sep 2026 04:54:44 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4567,39 +4269,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Sun, 20 Sep 2026 14:23:10 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
 Balance paid on your Amazon seller account
@@ -4622,39 +4324,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Sat, 19 Sep 2026 04:50:14 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4670,39 +4372,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Fri, 18 Sep 2026 05:13:12 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4718,39 +4420,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Thu, 17 Sep 2026 04:57:09 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4766,39 +4468,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 07:03:28 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4814,39 +4516,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 09:36:39 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4862,39 +4564,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Sun, 20 Sep 2026 05:13:35 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>"Amazon.it" &lt;store-news@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Il tuo carrello chiama</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.it/gp/cart/view.html?ref_=cor
 Pista ferroviaria elettrica a cubi da 145 pezzi, set trenino 3D antigravità, gioco fai da te per costruire percorsi, giocattolo educativo STEM e idea regalo creativa per bambini da 3 a 8 anni
@@ -4915,39 +4617,95 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 7 Oct 2026 14:20:27 +0000</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Rettifica del saldo negativo nei tuoi account</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Abbiamo rettificato il tuo saldo negativo di 31.62 € dovuto dal tuo account venditore Amazon.it in data ottobre 7, 2026, utilizzando i fondi disponibili nel tuo account Amazon.fr. Puoi visualizzare il saldo del tuo account in qualsiasi momento accedendo al tuo account e quindi alla dashboard dei pagamenti .
+Per maggiori informazioni, vai a Rettifica del saldo negativo nei tuoi account .
+Distinti saluti,
+Amazon Payments Europe
+ Segnala un problema con questa e-mail
+ Per qualsiasi domanda consulta: Seller Central
+ Per modificare le preferenze sulle e-mail consulta: Preferenze sulle notifiche
+ Copyright 2026 Amazon, Inc. o società affiliate. Tutti i diritti riservati.
+ Amazon Payments Europe
+ 38 avenue John F. Kennedy,
+ L-1855 Lussemburgo,
+ Numero di registrazione in Lussemburgo: B-101818,
+ Capitale Sociale 165.833 EUR,
+ Numero di licenza di attività commerciale: 134248,
+ Partita IVA n. LU 20260743.
+ Questa e-mail è stata inviata da un indirizzo e-mail non monitorato.
+ SPC-EUAmazon-1600890628109755</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Wed, 7 Oct 2026 05:12:07 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>您的亚马逊卖家账户支付的余额</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>96
 您的亚马逊卖家账户支付的余额
@@ -4976,39 +4734,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Sun, 4 Oct 2026 13:38:25 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5028,39 +4786,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Fri, 2 Oct 2026 23:31:42 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -5080,39 +4838,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Thu, 1 Oct 2026 14:51:16 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -5128,39 +4886,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 13:36:40 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5180,39 +4938,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 13:33:11 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -5232,39 +4990,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 00:41:51 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -5284,39 +5042,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 12:37:44 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -5333,39 +5091,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Mon, 21 Sep 2026 17:07:48 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Ver el informe fiscal de China de abril a junio de 2026</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
  Presentamos tu declaración fiscal trimestral a la autoridad tributaria china. Ya puedes descargar la declaración para consultarla.
@@ -5381,39 +5139,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Mon, 21 Sep 2026 13:27:57 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Last chance to register for Amazon Accelerate 2026</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-11/7z5qvbd/6900257597/h/DNy5vrd2KmewvkDHEulcRelQOUFu36-wIzMILRKLzn4)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5qvbh/6900257597/h/DNy5vrd2KmewvkDHEulcRelQOUFu36-wIzMILRKLzn4)
@@ -5428,39 +5186,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Sun, 20 Sep 2026 14:07:50 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5480,39 +5238,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Thu, 17 Sep 2026 12:34:14 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Registration closes this Friday—save $200 with your exclusive code</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-15/7z5szk3/6892578632/h/_CYRbTDGVtA_TsyRgyvyoHjCej_EjJw20h52f6bfhUo)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5szk6/6892578632/h/_CYRbTDGVtA_TsyRgyvyoHjCej_EjJw20h52f6bfhUo)
@@ -5526,39 +5284,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 12:07:50 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Strategies built for sellers at your stage—plus $200 off</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-10/7z5qrvp/6889941143/h/MQuKVqSCTubvlftYjmZsRYwIhpcMmpopXweaNOtgp5c)
 [Secure your spot](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5qrvs/6889941143/h/MQuKVqSCTubvlftYjmZsRYwIhpcMmpopXweaNOtgp5c)
@@ -5572,39 +5330,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 15:16:31 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5624,39 +5382,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 14:49:51 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5673,39 +5431,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 13:38:38 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5725,137 +5483,89 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 14 Sep 2026 13:11:23 +0000</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>The Accelerate 2026 agenda got even better. See what's new.</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-04/7z5l4gm/6885907415/h/1g4K0sP-fwBdUvnQHTI9XLWTzXNhSmHYs6__l_Evdwk)
-[Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5l4gq/6885907415/h/1g4K0sP-fwBdUvnQHTI9XLWTzXNhSmHYs6__l_Evdwk)
-New content. Same packed lineup. More reasons to be there.
-The Amazon Accelerate 2026 agenda keeps getting better. We've added new sessions and experiences we think you’ll love.
-[Register now](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5l4gq/6885907415/h/1g4K0sP-fwBdUvnQHTI9XLWTzXNhSmHYs6__l_Evdwk)
-Here's what's new on the agenda:
-- AI tools you can use today
-New sessions on how to use AI-powered tools for listing creation, A+ Content optimization, and inventory planning—with step-by-step guidance you can apply immediately.
-- Brand building programs
-Learn how to use Brand Registry, A+ Content, and Brand Tailored Promotions to protect and grow your brand.
-- Account health essentials
-New workshops on proactively managing your account health, understanding policies, and staying in good standing—so you can focus on growing instead of troubleshooting.
-- W</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 6 Oct 2026 13:03:41 +0000</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
-        </is>
-      </c>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon-Fulfilled Inventory - Action Required</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>Dear Seller,
-You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
-Please create a removal request for the ASIN(s) listed below to have your inventory sent to a location of your choice. If this inventory is not removed within 30 days of this notification (by 04/11/2026), we shall dispose of it in accordance with our FBA policies.
-For more information regarding the removal of this product, see the notification e-mail you received from our Seller Performance Team.
-Thank you for your prompt attention to this matter.
-Yours faithfully,
-Fulfilment by Amazon Team
-Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
-Affected Product(s):
-B0FD8VC559
- SPC-EUAmazon-1600890627600107</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 7 Oct 2026 13:15:21 +0000</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai EU,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listing?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
+-
+ If you believe that your products are exempt from these requirements, submit documentation demonstrating why they are not subj</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 6 Oct 2026 10:13:01 +0000</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 7 Oct 2026 11:16:06 +0000</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5873,39 +5583,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 5 Oct 2026 22:52:24 +0000</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 7 Oct 2026 10:16:15 +0000</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5923,39 +5633,87 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 5 Oct 2026 14:42:52 +0000</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 6 Oct 2026 13:03:41 +0000</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon-Fulfilled Inventory - Action Required</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Dear Seller,
+You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
+Please create a removal request for the ASIN(s) listed below to have your inventory sent to a location of your choice. If this inventory is not removed within 30 days of this notification (by 04/11/2026), we shall dispose of it in accordance with our FBA policies.
+For more information regarding the removal of this product, see the notification e-mail you received from our Seller Performance Team.
+Thank you for your prompt attention to this matter.
+Yours faithfully,
+Fulfilment by Amazon Team
+Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
+Affected Product(s):
+B0FD8VC559
+ SPC-EUAmazon-1600890627600107</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 6 Oct 2026 10:13:01 +0000</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5973,39 +5731,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 3 Oct 2026 22:29:49 +0000</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 5 Oct 2026 22:52:24 +0000</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6023,39 +5781,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 2 Oct 2026 19:40:11 +0000</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 5 Oct 2026 14:42:52 +0000</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6073,39 +5831,139 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 3 Oct 2026 22:29:49 +0000</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai EU,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 2 Oct 2026 19:40:11 +0000</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai EU,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Wed, 30 Sep 2026 10:06:35 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -6123,39 +5981,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Tue, 29 Sep 2026 10:06:26 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -6173,39 +6031,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Tue, 29 Sep 2026 05:31:39 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>重要通知｜9月1日起，Pan-EU入库欧盟及直接发往法国的货件必须提供进口详情</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>未提供 MRN+EORI 将无法创建新货件，请在收货后 60 天内完成补全
 尊敬的 深圳市微海众信科技有限公司,
@@ -6233,39 +6091,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Mon, 28 Sep 2026 10:05:46 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hello Weihai CA,
@@ -6284,39 +6142,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Sun, 27 Sep 2026 10:05:10 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hello Weihai CA,
@@ -6335,39 +6193,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 01:10:33 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6385,39 +6243,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 01:07:50 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6435,39 +6293,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 14:57:06 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Zwrot kosztów zgodności z wymogami w zakresie opakowań w ramach ROP</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
  Dokończenie rejestracji w ramach ROP i uzyskanie częściowego zwrotu kosztów w Polsce
@@ -6484,39 +6342,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 14:07:32 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -6534,39 +6392,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 10:28:03 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Få ersättning för kostnader för överensstämmelse med EPR-förpackningar</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
  Slutför EPR-registreringen och få en del av kostnaderna återbetalda i Sverige
@@ -6584,39 +6442,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 10:08:29 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -6635,39 +6493,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 10:08:17 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -6686,39 +6544,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Tue, 22 Sep 2026 07:40:02 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>"pli-cn-seller-compliance@amazon.com" &lt;pli-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 22191892721] [立刻采取行动购买或更新商业责任险]</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 22191892721] [立刻采取行动购买或更新商业责任险]
@@ -6748,39 +6606,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Fri, 18 Sep 2026 15:44:09 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>cscompliance-docreview-seller@amazon.de</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Problem gelöst (Anfrage Nr.: 13280404852)</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
 Problem gelöst (Anfrage Nr.: 13280404852)
@@ -6802,41 +6660,41 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Fri, 18 Sep 2026 15:42:38 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 13280404852] SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY,
  MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document
  Review</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 13280404852] SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review
@@ -6854,40 +6712,40 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Fri, 18 Sep 2026 08:56:32 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review
@@ -6912,39 +6770,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 07:08:09 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号
@@ -6971,40 +6829,40 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 20:32:42 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Submit proof of insurance by January 18 to avoid listing
  deactivation</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
  Review your impacted products and categories and submit proof of insurance before January 18, 2027 to avoid listing deactivation.
@@ -7020,10 +6878,155 @@
         </is>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 7 Oct 2026 13:15:49 +0000</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Dien productveiligheidsdocumentatie in om productvermeldingen
+ opnieuw te activeren</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
+ Hallo Weihai EU,
+ Sommige van je productvermeldingen zijn gedeactiveerd omdat er verplichte nalevingsvereisten voor je producten ontbreken. Bekijk de gegevens en de stappen hieronder. De betreffende productvermeldingen worden aan het einde van deze e-mail weergegeven.
+ Waarom gebeurt dit?
+ We hebben deze actie ondernomen omdat voor deze producten verplichte nalevingsinformatie ontbreekt. Raadpleeg onze hulp-pagina Productveiligheid en -conformiteit voor informatie over de toepasselijke wet- en regelgeving en het Amazon-beleid. We hebben gebruikgemaakt van een combinatie van geautomatiseerde middelen en deskundige menselijke beoordeling om dit probleem te identificeren en deze beslissing te nemen.
+ De tabel aan het einde van deze e-mail bevat productspecifieke nalevingsvereisten.
+ Hoe activeer ik mijn productvermeldingen opnieuw?
+ Als je de vereiste nalevingsgegevens wilt verstrekken, ga je naar de pagina Accountstatus en zoek je de aanvragen voor productconformiteit:
+-
+ Als je over de vereiste documentatie beschikt, volg je de instructies om je nalevingsdocumenten in te dienen. We zullen alleen </t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 7 Oct 2026 13:15:41 +0000</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Presenta la documentación sobre seguridad del producto para reactivar los listings
+ Hola, Weihai EU:
+ Algunos de tus listings se han desactivado debido a que tus productos no cumplen los requisitos obligatorios. Revisa a continuación los detalles y siguientes pasos. Los listings afectados aparecen al final de este correo electrónico.
+ ¿A qué se debe esto?
+ Tomamos esta medida porque a estos productos les falta información de cumplimiento normativo obligatoria. Para más información sobre las leyes, normativas y políticas de Amazon aplicables, consulta Cumplimiento y seguridad de los productos . Hemos usado una combinación de medios automatizados y revisión humana experta para identificar la incidencia y tomar una decisión.
+ En la tabla que aparece al final de este correo electrónico se proporcionan los requisitos de cumplimiento normativo específicos del producto.
+ ¿Cómo puedo reactivar mis listings?
+ Para proporcionar la información de cumplimiento normativo obligatoria, ve a la página Estado de la cuenta y localiza las solicitudes de cumplimiento normativo del producto:
+-
+ Si dispones de la documentación obligatoria, sigue las instrucciones para presentar los documentos de cum</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 7 Oct 2026 13:15:40 +0000</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
+ Bonjour Weihai EU,
+ Certaines de vos mises en vente ont été désactivées, car vos produits ne respectaient pas des exigences de conformité obligatoires. Consultez les détails et les étapes suivantes ci-dessous. Les produits mis en vente concernés figurent à la fin de cet e-mail.
+ Pourquoi cela se produit-il ?
+ Nous prenons cette mesure, car ces produits ne présentent pas les informations de conformité obligatoires. Consultez notre page d’aide Sécurité et conformité des produits pour obtenir des informations sur les lois, réglementations et politiques Amazon applicables. Nous nous sommes appuyés sur une combinaison de moyens automatisés et de contrôles menés par des personnes expérimentées pour identifier ce problème et prendre cette décision.
+ Le tableau situé à la fin de cet e-mail présente les exigences de conformité spécifiques aux produits.
+ Comment réactiver mes produits mis en vente ?
+ Pour fournir les informations de conformité requises, accédez à la page État du compte et localisez les demandes de conformité des produits :
+-
+ Si vous disposez des documents requis, suivez les instructio</t>
+        </is>
+      </c>
+    </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -7038,37 +7041,34 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Mon, 14 Sep 2026 05:40:35 +0000</t>
+          <t>Wed, 7 Oct 2026 13:15:09 +0000</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE:
- A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
+          <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
+ le offerte</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr"/>
       <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
-SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review
- Do not reply back to this e-mail!
-Hello,
-Thank you for submitting a document to the Chemical Safety Compliance Team.
-Your product is a kit/set/pack. A Safety Data Sheet is required for each possible hazardous product from the kit/set/pack, as indicated below:
-color acrylic paint;
-Ceramic clay
-● We already received a compliant documentation for "color acrylic paint"
-● The document uploaded for "Ceramic clay" is incomplete, inaccurate or otherwise conflicting, and cannot be used for classification. Specifically:
-→ The SDS does not match the ( branding/manufacturer/logo of the product ):
-The manufacturer/brand/logo of the product on the SDS is "Eternity Commerce LTD" while the listing manufacturer/brand/logo of the product is "Roaxkois".
-Until we receive the entire valid documentation, for all the possible hazardous products from the kit/set/pack, the hazard warnings for your products may not appear on the ASIN's product detail page and your products may be rejected by some fulfillment centers.
-For guidance on Safety Data Sheet requirements, please refer to https</t>
+ Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
+ Gentile Weihai EU,
+ Alcune delle tue offerte sono state disattivate a causa della mancanza di alcuni requisiti di conformità obbligatori per i tuoi prodotti. Rivedi i dettagli e i passi successivi riportati di seguito. Puoi visualizzare le offerte interessate in fondo a questa e-mail.
+ Ciò a cosa è dovuto?
+ Abbiamo intrapreso questo provvedimento in quanto i tuoi prodotti non dispongono delle informazioni obbligatorie sulla conformità. Consulta la pagina di aiuto Sicurezza e conformità dei prodotti per informazioni sulle leggi, le normative e le politiche di Amazon applicabili. Questa decisione è stata presa sulla base dei risultati di un'analisi effettuata in parte tramite revisione umana e in parte per mezzo di sistemi automatizzati.
+ La tabella alla fine di questa e-mail contiene i requisiti di conformità specifici per i prodotti.
+ Come faccio a riattivare le mie offerte?
+ Per fornire le informazioni di conformità richieste, vai alla pagina Stato dell'account per individuare le richieste di conformità dei prodotti:
+-
+ Se disponi della documentazione richiesta, segui le istruzioni per inviare i do</t>
         </is>
       </c>
     </row>
@@ -12976,53 +12976,6 @@
         </is>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B245" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C245" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D245" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 14 Sep 2026 14:01:06 +0000</t>
-        </is>
-      </c>
-      <c r="E245" s="2" t="inlineStr">
-        <is>
-          <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F245" s="2" t="inlineStr">
-        <is>
-          <t>Redesigned Seller Central becomes default 24 Sep</t>
-        </is>
-      </c>
-      <c r="G245" s="2" t="inlineStr"/>
-      <c r="H245" s="2" t="inlineStr">
-        <is>
-          <t>96
- Same powerful tools, built to grow with your business.
- Hello,
- As of 24 September 2026, you’ll be welcomed back to the new Seller Central, a selling experience shaped by feedback from seller like you. Since you last tried the new Seller Central experience, we’ve made meaningful improvements based on your input.
- We've streamlined navigation to make your daily tools easier to access. Product and shipment management now feature faster search and side-panel details. Seller Assistant is built into Manage Products to surface insights and take actions on your behalf. Plus, customisable workspaces let you choose what data to see and save your preferred views.
- To get familiar with the new Seller Central experience and to find all the tools you need:
-- Get to know the new layout with the full guide to finding your favourite tools .
-- Discover every tool and page in one place with the site MAP , also accessible at the bottom left corner of the menu.
-- Locate any tool instantly using the search bar at the top of any page.
-- Stay on top of what matters with the Action Center in the left panel for your most important next STEP across all workspaces. You can still access classic Seller Cen</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
